--- a/invoices.xlsx
+++ b/invoices.xlsx
@@ -413,36 +413,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>S No</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Invoice No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>UID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Course</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
@@ -451,310 +456,396 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>100001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>INV-0194705760</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>32095838547235</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Karthik k</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Corporate Lawyer Launchpad</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>4999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>100002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>INV-194705761</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="n">
         <v>32095838547236</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Karthik k</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Corporate Lawyer Launchpad</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>4999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>100003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>INV-194705762</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" t="n">
         <v>32095838547237</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Karthik k</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Corporate Lawyer Launchpad</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>4999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>100004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>INV-194705763</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="n">
         <v>32095838547238</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Karthik k</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Corporate Lawyer Launchpad</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>4999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>100005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>INV-194705764</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" t="n">
         <v>32095838547239</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Karthik k</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Corporate Lawyer Launchpad</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>4999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>100006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>INV-194705765</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="n">
         <v>32095838547240</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Karthik k</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Corporate Lawyer Launchpad</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>4999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>100007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>INV-194705766</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" t="n">
         <v>32095838547241</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Karthik k</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Corporate Lawyer Launchpad</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>4999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>100008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>INV-194705767</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" t="n">
         <v>32095838547242</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Karthik k</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Corporate Lawyer Launchpad</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>4999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>100009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>INV-194705768</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" t="n">
         <v>32095838547243</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>K Karthik</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>All Access Pack</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>100010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>INV-194705769</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="C11" t="n">
         <v>32095838547244</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>K Karthik</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Architecture Launchpad</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>5999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>100011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>INV-194705770</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>32095838547245</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" t="n">
+        <v>32095838547245</v>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>K Karthik</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Architecture Launchpad</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
+        <v>5999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>INV-194705771</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>32095838547246</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>K Karthik</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Architecture Launchpad</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
         <v>5999</v>
       </c>
     </row>
